--- a/processos_resultado.xlsx
+++ b/processos_resultado.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E39"/>
+  <dimension ref="A1:C38"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -409,12 +409,6 @@
       <c r="C1" t="str">
         <v>check</v>
       </c>
-      <c r="D1" t="str">
-        <v/>
-      </c>
-      <c r="E1" t="str">
-        <v/>
-      </c>
     </row>
     <row r="2">
       <c r="A2">
@@ -426,12 +420,6 @@
       <c r="C2" t="str">
         <v>nao</v>
       </c>
-      <c r="D2" t="str">
-        <v/>
-      </c>
-      <c r="E2" t="str">
-        <v/>
-      </c>
     </row>
     <row r="3">
       <c r="A3">
@@ -443,12 +431,6 @@
       <c r="C3" t="str">
         <v>nao</v>
       </c>
-      <c r="D3" t="str">
-        <v/>
-      </c>
-      <c r="E3" t="str">
-        <v/>
-      </c>
     </row>
     <row r="4">
       <c r="A4">
@@ -460,12 +442,6 @@
       <c r="C4" t="str">
         <v>nao</v>
       </c>
-      <c r="D4" t="str">
-        <v/>
-      </c>
-      <c r="E4" t="str">
-        <v/>
-      </c>
     </row>
     <row r="5">
       <c r="A5">
@@ -477,12 +453,6 @@
       <c r="C5" t="str">
         <v>nao</v>
       </c>
-      <c r="D5" t="str">
-        <v/>
-      </c>
-      <c r="E5" t="str">
-        <v/>
-      </c>
     </row>
     <row r="6">
       <c r="A6">
@@ -494,12 +464,6 @@
       <c r="C6" t="str">
         <v>nao</v>
       </c>
-      <c r="D6" t="str">
-        <v/>
-      </c>
-      <c r="E6" t="str">
-        <v/>
-      </c>
     </row>
     <row r="7">
       <c r="A7">
@@ -511,12 +475,6 @@
       <c r="C7" t="str">
         <v>nao</v>
       </c>
-      <c r="D7" t="str">
-        <v/>
-      </c>
-      <c r="E7" t="str">
-        <v/>
-      </c>
     </row>
     <row r="8">
       <c r="A8">
@@ -528,12 +486,6 @@
       <c r="C8" t="str">
         <v>nao</v>
       </c>
-      <c r="D8" t="str">
-        <v/>
-      </c>
-      <c r="E8" t="str">
-        <v/>
-      </c>
     </row>
     <row r="9">
       <c r="A9">
@@ -545,12 +497,6 @@
       <c r="C9" t="str">
         <v>nao</v>
       </c>
-      <c r="D9" t="str">
-        <v/>
-      </c>
-      <c r="E9" t="str">
-        <v/>
-      </c>
     </row>
     <row r="10">
       <c r="A10">
@@ -562,12 +508,6 @@
       <c r="C10" t="str">
         <v>nao</v>
       </c>
-      <c r="D10" t="str">
-        <v/>
-      </c>
-      <c r="E10" t="str">
-        <v/>
-      </c>
     </row>
     <row r="11">
       <c r="A11">
@@ -579,12 +519,6 @@
       <c r="C11" t="str">
         <v>nao</v>
       </c>
-      <c r="D11" t="str">
-        <v/>
-      </c>
-      <c r="E11" t="str">
-        <v/>
-      </c>
     </row>
     <row r="12">
       <c r="A12">
@@ -596,12 +530,6 @@
       <c r="C12" t="str">
         <v>nao</v>
       </c>
-      <c r="D12" t="str">
-        <v/>
-      </c>
-      <c r="E12" t="str">
-        <v/>
-      </c>
     </row>
     <row r="13">
       <c r="A13">
@@ -613,12 +541,6 @@
       <c r="C13" t="str">
         <v>nao</v>
       </c>
-      <c r="D13" t="str">
-        <v/>
-      </c>
-      <c r="E13" t="str">
-        <v/>
-      </c>
     </row>
     <row r="14">
       <c r="A14">
@@ -630,12 +552,6 @@
       <c r="C14" t="str">
         <v>nao</v>
       </c>
-      <c r="D14" t="str">
-        <v/>
-      </c>
-      <c r="E14" t="str">
-        <v/>
-      </c>
     </row>
     <row r="15">
       <c r="A15">
@@ -647,12 +563,6 @@
       <c r="C15" t="str">
         <v>nao</v>
       </c>
-      <c r="D15" t="str">
-        <v/>
-      </c>
-      <c r="E15" t="str">
-        <v/>
-      </c>
     </row>
     <row r="16">
       <c r="A16">
@@ -664,12 +574,6 @@
       <c r="C16" t="str">
         <v>nao</v>
       </c>
-      <c r="D16" t="str">
-        <v/>
-      </c>
-      <c r="E16" t="str">
-        <v/>
-      </c>
     </row>
     <row r="17">
       <c r="A17">
@@ -681,12 +585,6 @@
       <c r="C17" t="str">
         <v>nao</v>
       </c>
-      <c r="D17" t="str">
-        <v/>
-      </c>
-      <c r="E17" t="str">
-        <v/>
-      </c>
     </row>
     <row r="18">
       <c r="A18">
@@ -698,12 +596,6 @@
       <c r="C18" t="str">
         <v>nao</v>
       </c>
-      <c r="D18" t="str">
-        <v/>
-      </c>
-      <c r="E18" t="str">
-        <v/>
-      </c>
     </row>
     <row r="19">
       <c r="A19">
@@ -715,12 +607,6 @@
       <c r="C19" t="str">
         <v>nao</v>
       </c>
-      <c r="D19" t="str">
-        <v/>
-      </c>
-      <c r="E19" t="str">
-        <v/>
-      </c>
     </row>
     <row r="20">
       <c r="A20">
@@ -732,12 +618,6 @@
       <c r="C20" t="str">
         <v>nao</v>
       </c>
-      <c r="D20" t="str">
-        <v/>
-      </c>
-      <c r="E20" t="str">
-        <v/>
-      </c>
     </row>
     <row r="21">
       <c r="A21">
@@ -749,12 +629,6 @@
       <c r="C21" t="str">
         <v>nao</v>
       </c>
-      <c r="D21" t="str">
-        <v/>
-      </c>
-      <c r="E21" t="str">
-        <v/>
-      </c>
     </row>
     <row r="22">
       <c r="A22">
@@ -766,12 +640,6 @@
       <c r="C22" t="str">
         <v>nao</v>
       </c>
-      <c r="D22" t="str">
-        <v/>
-      </c>
-      <c r="E22" t="str">
-        <v/>
-      </c>
     </row>
     <row r="23">
       <c r="A23">
@@ -781,13 +649,7 @@
         <v>60041.000037/2026-21</v>
       </c>
       <c r="C23" t="str">
-        <v>verificar</v>
-      </c>
-      <c r="D23" t="str">
-        <v/>
-      </c>
-      <c r="E23" t="str">
-        <v/>
+        <v>nao</v>
       </c>
     </row>
     <row r="24">
@@ -800,12 +662,6 @@
       <c r="C24" t="str">
         <v>nao</v>
       </c>
-      <c r="D24" t="str">
-        <v/>
-      </c>
-      <c r="E24" t="str">
-        <v/>
-      </c>
     </row>
     <row r="25">
       <c r="A25">
@@ -817,12 +673,6 @@
       <c r="C25" t="str">
         <v>nao</v>
       </c>
-      <c r="D25" t="str">
-        <v/>
-      </c>
-      <c r="E25" t="str">
-        <v/>
-      </c>
     </row>
     <row r="26">
       <c r="A26">
@@ -834,12 +684,6 @@
       <c r="C26" t="str">
         <v>nao</v>
       </c>
-      <c r="D26" t="str">
-        <v/>
-      </c>
-      <c r="E26" t="str">
-        <v/>
-      </c>
     </row>
     <row r="27">
       <c r="A27">
@@ -851,12 +695,6 @@
       <c r="C27" t="str">
         <v>nao</v>
       </c>
-      <c r="D27" t="str">
-        <v/>
-      </c>
-      <c r="E27" t="str">
-        <v/>
-      </c>
     </row>
     <row r="28">
       <c r="A28">
@@ -868,12 +706,6 @@
       <c r="C28" t="str">
         <v>nao</v>
       </c>
-      <c r="D28" t="str">
-        <v/>
-      </c>
-      <c r="E28" t="str">
-        <v/>
-      </c>
     </row>
     <row r="29">
       <c r="A29">
@@ -885,12 +717,6 @@
       <c r="C29" t="str">
         <v>nao</v>
       </c>
-      <c r="D29" t="str">
-        <v/>
-      </c>
-      <c r="E29" t="str">
-        <v/>
-      </c>
     </row>
     <row r="30">
       <c r="A30">
@@ -902,12 +728,6 @@
       <c r="C30" t="str">
         <v>nao</v>
       </c>
-      <c r="D30" t="str">
-        <v/>
-      </c>
-      <c r="E30" t="str">
-        <v/>
-      </c>
     </row>
     <row r="31">
       <c r="A31">
@@ -919,12 +739,6 @@
       <c r="C31" t="str">
         <v>nao</v>
       </c>
-      <c r="D31" t="str">
-        <v/>
-      </c>
-      <c r="E31" t="str">
-        <v/>
-      </c>
     </row>
     <row r="32">
       <c r="A32">
@@ -936,12 +750,6 @@
       <c r="C32" t="str">
         <v>nao</v>
       </c>
-      <c r="D32" t="str">
-        <v/>
-      </c>
-      <c r="E32" t="str">
-        <v/>
-      </c>
     </row>
     <row r="33">
       <c r="A33">
@@ -953,12 +761,6 @@
       <c r="C33" t="str">
         <v>nao</v>
       </c>
-      <c r="D33" t="str">
-        <v/>
-      </c>
-      <c r="E33" t="str">
-        <v/>
-      </c>
     </row>
     <row r="34">
       <c r="A34">
@@ -970,12 +772,6 @@
       <c r="C34" t="str">
         <v>nao</v>
       </c>
-      <c r="D34" t="str">
-        <v/>
-      </c>
-      <c r="E34" t="str">
-        <v/>
-      </c>
     </row>
     <row r="35">
       <c r="A35">
@@ -987,12 +783,6 @@
       <c r="C35" t="str">
         <v>nao</v>
       </c>
-      <c r="D35" t="str">
-        <v/>
-      </c>
-      <c r="E35" t="str">
-        <v/>
-      </c>
     </row>
     <row r="36">
       <c r="A36">
@@ -1004,12 +794,6 @@
       <c r="C36" t="str">
         <v>nao</v>
       </c>
-      <c r="D36" t="str">
-        <v/>
-      </c>
-      <c r="E36" t="str">
-        <v/>
-      </c>
     </row>
     <row r="37">
       <c r="A37">
@@ -1021,12 +805,6 @@
       <c r="C37" t="str">
         <v>nao</v>
       </c>
-      <c r="D37" t="str">
-        <v/>
-      </c>
-      <c r="E37" t="str">
-        <v/>
-      </c>
     </row>
     <row r="38">
       <c r="A38">
@@ -1038,33 +816,10 @@
       <c r="C38" t="str">
         <v>nao</v>
       </c>
-      <c r="D38" t="str">
-        <v/>
-      </c>
-      <c r="E38" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39">
-        <v>41</v>
-      </c>
-      <c r="B39" t="str">
-        <v>60041.000037/2026-21</v>
-      </c>
-      <c r="C39" t="str">
-        <v>verificar</v>
-      </c>
-      <c r="D39" t="str">
-        <v/>
-      </c>
-      <c r="E39" t="str">
-        <v/>
-      </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:E39"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:C38"/>
   </ignoredErrors>
 </worksheet>
 </file>